--- a/Alinacak Malzemeler Ucuz.xlsx
+++ b/Alinacak Malzemeler Ucuz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erayfazilordanuc/Projects/RC Uçak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EDCBB9-9C6F-A746-857A-5E325BB6B280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE42DAA-39BF-F84F-85AC-7AFC7AD7A5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="85">
   <si>
     <t>Fotoblok RC Trainer - Alinacak Malzemeler</t>
   </si>
@@ -50,6 +50,9 @@
     <t>Fiyatlar Agustos 2026 tahminidir; siparis oncesi guncel fiyat kontrol edilmelidir.</t>
   </si>
   <si>
+    <t>OK</t>
+  </si>
+  <si>
     <t>Malzeme</t>
   </si>
   <si>
@@ -101,24 +104,6 @@
     <t>Ara toplam</t>
   </si>
   <si>
-    <t>Servo tel tutucu (rushpod) 1.5 mm</t>
-  </si>
-  <si>
-    <t>Rudder ve elevator icin</t>
-  </si>
-  <si>
-    <t>https://www.robocombo.com/servo-tel-tutucu-1.5mm-rushpod-baglanti-aparati-3740</t>
-  </si>
-  <si>
-    <t>Servo rod teli 1.5 mm x 500 mm</t>
-  </si>
-  <si>
-    <t>Iki ucu vidali</t>
-  </si>
-  <si>
-    <t>https://www.thkmodelucak.com/urun/tel-iki-ucu-vidali-1-5mm-500mm</t>
-  </si>
-  <si>
     <t>3S 1500 mAh LiPo batarya</t>
   </si>
   <si>
@@ -134,6 +119,9 @@
     <t>1.6 A, 2-3S. Tek pil icin B6AC gereksiz; B6AC en ucuz 1433 TL</t>
   </si>
   <si>
+    <t>https://www.direnc.net/3s-40a-lipo-pil-sarj-devresi-modulu</t>
+  </si>
+  <si>
     <t>LiPo hucre voltaj gostergesi (1-8S)</t>
   </si>
   <si>
@@ -149,7 +137,13 @@
     <t>https://www.robotzade.com/urun/lipo-pil-yanmaz-koruma-cantasi-lipo-safe-bag-23x30cm</t>
   </si>
   <si>
-    <t>1045 multirotor pervanesi degil; daha az akim ceker</t>
+    <t>Haoye 8x6 EP pervane (8060)</t>
+  </si>
+  <si>
+    <t>9x6 stokta yok; 8x6 A2212+3S icin ~14 A, daha uygun</t>
+  </si>
+  <si>
+    <t>https://www.hobbyrcmodels.com/urun/haoye-8x6-ep-pervane-8060-beyaz-d-6mm-h-10-5mm-6-75gr-1</t>
   </si>
   <si>
     <t>16 AWG silikon kablo 1 m</t>
@@ -185,16 +179,10 @@
     <t>https://www.robotzade.com/urun/xt60-disi-lipo-pil-konnektor</t>
   </si>
   <si>
-    <t>STM32 Black Pill F411</t>
-  </si>
-  <si>
-    <t>Bir verici bir alici tarafi icin</t>
-  </si>
-  <si>
-    <t>ST-Link V2 programlayici</t>
-  </si>
-  <si>
-    <t>https://www.robotzade.com/urun/st-link-v2-mini-programlayici</t>
+    <t>STM32F411CEU6 Black Pill</t>
+  </si>
+  <si>
+    <t>https://www.f1depo.com/urun/stm32f411ceu6-black-pill-100mhz-512kb-gelistirme-karti</t>
   </si>
   <si>
     <t>GENEL TOPLAM (satin alinacak)</t>
@@ -257,6 +245,9 @@
     <t>NOTLAR</t>
   </si>
   <si>
+    <t>OK sutunu: karar verilmis ve siparise hazir kalemler isaretlidir.</t>
+  </si>
+  <si>
     <t>Mavi yazili hucreler elle girilen fiyatlardir; guncelledikce toplamlar kendiliginden yenilenir.</t>
   </si>
   <si>
@@ -290,40 +281,16 @@
     <t>nRF24 icin ayri adaptor karti listeye eklenmedi; modulun VCC-GND ucuna 10 uF + 100 nF lehimlemek ayni isi goruyor.</t>
   </si>
   <si>
-    <t>https://www.robocombo.com/imax-b3-pro-1s-3s-lipo-sarj-aleti-3533?srsltid=AfmBOoomlxkTrgpVDz7CRcHKjgj-BRW4d5guumT5_fu1gM9X5iSR5Z8g7ro</t>
-  </si>
-  <si>
-    <t>Link 2</t>
-  </si>
-  <si>
-    <t>https://www.robotzade.com/urun/lipo-pil-test-cihazi-lipo-voltaj-olcer-lipo-alarm?srsltid=AfmBOoqctNwqcSxvfUqclNrSNPGfUeQ5kw_ZUTjN7xMEexRFc5Szh_m3-Ss</t>
-  </si>
-  <si>
-    <t>https://www.hobbyrcmodels.com/urun/haoye-8x6-ep-pervane-8060-beyaz-d-6mm-h-10-5mm-6-75gr-1</t>
-  </si>
-  <si>
-    <t>8x6 ucak pervanesi</t>
-  </si>
-  <si>
-    <t>https://www.trendyol.com/boss-tape/ip-takviyeli-cok-guclu-koli-bandi-en-25mm-boy-25mt-p-229367383?boutiqueId=61&amp;merchantId=153414&amp;storefrontId=1&amp;countryCode=TR&amp;language=tr&amp;gads=true</t>
+    <t>GUC SISTEMI</t>
+  </si>
+  <si>
+    <t>YAPI MALZEMELERI</t>
+  </si>
+  <si>
+    <t>KUMANDA LINKI ELEKTRONIGI</t>
   </si>
   <si>
     <t>ELINDE MEVCUT - SATIN ALINMAYACAK</t>
-  </si>
-  <si>
-    <t>KUMANDA LINKI ELEKTRONIGI</t>
-  </si>
-  <si>
-    <t>GUC SISTEMI</t>
-  </si>
-  <si>
-    <t>KUMANDA MEKANIGI</t>
-  </si>
-  <si>
-    <t>YAPI MALZEMELERI</t>
-  </si>
-  <si>
-    <t>https://www.robotistan.com/stm32-f411ceu6-gelistirme-karti?language=tr&amp;h=92227170</t>
   </si>
 </sst>
 </file>
@@ -333,18 +300,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot; TL&quot;"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -388,6 +350,13 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1B5E20"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -426,13 +395,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF1B5E20"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -443,16 +405,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -469,6 +423,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDCE6EC"/>
         <bgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E6C9"/>
+        <bgColor rgb="FFDCE6EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -514,21 +474,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -539,21 +501,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -594,8 +556,8 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFDCE6EC"/>
+      <rgbColor rgb="FFC8E6C9"/>
       <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -816,16 +778,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="46" customWidth="1"/>
-    <col min="7" max="7" width="44" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="46" customWidth="1"/>
+    <col min="8" max="8" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
@@ -871,802 +834,753 @@
         <v>10</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="6"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="9">
+        <v>4</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="10">
         <v>3</v>
       </c>
-      <c r="C8" s="10">
+      <c r="D8" s="11">
         <v>100</v>
       </c>
-      <c r="D8" s="11">
-        <f t="shared" ref="D8:D10" si="0">B8*C8</f>
+      <c r="E8" s="12">
+        <f t="shared" ref="E8:E10" si="0">C8*D8</f>
         <v>300</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="9" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>14</v>
       </c>
+      <c r="H8" s="14" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="9">
+        <v>4</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="10">
         <v>1</v>
       </c>
-      <c r="C9" s="10">
+      <c r="D9" s="11">
         <v>67</v>
       </c>
-      <c r="D9" s="11">
+      <c r="E9" s="12">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>16</v>
+      <c r="F9" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="H9" s="14" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="9">
+        <v>4</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="10">
         <v>1</v>
       </c>
-      <c r="C10" s="10">
+      <c r="D10" s="11">
         <v>80</v>
       </c>
-      <c r="D10" s="11">
+      <c r="E10" s="12">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>89</v>
-      </c>
+      <c r="F10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16">
-        <f>SUM(D8:D10)</f>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18">
+        <f>SUM(E8:E10)</f>
         <v>447</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="6"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="6"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="9">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="C14" s="10">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D14" s="11">
-        <f>B14*C14</f>
-        <v>60</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>22</v>
+        <v>800</v>
+      </c>
+      <c r="E14" s="12">
+        <f t="shared" ref="E14:E22" si="1">C14*D14</f>
+        <v>800</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>23</v>
       </c>
+      <c r="H14" s="14" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="9">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="C15" s="10">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D15" s="11">
-        <f>B15*C15</f>
-        <v>80</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>25</v>
+        <v>430</v>
+      </c>
+      <c r="E15" s="12">
+        <f t="shared" si="1"/>
+        <v>430</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>26</v>
       </c>
+      <c r="H15" s="14" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16">
-        <f>SUM(D14:D15)</f>
-        <v>140</v>
-      </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="9">
+      <c r="A16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="10">
         <v>1</v>
       </c>
-      <c r="C19" s="10">
-        <v>800</v>
-      </c>
-      <c r="D19" s="11">
-        <f t="shared" ref="D19:D27" si="1">B19*C19</f>
-        <v>800</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="9">
-        <v>1</v>
-      </c>
-      <c r="C20" s="10">
-        <v>430</v>
-      </c>
-      <c r="D20" s="11">
-        <f t="shared" si="1"/>
-        <v>430</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="9">
-        <v>1</v>
-      </c>
-      <c r="C21" s="10">
+      <c r="D16" s="11">
         <v>60</v>
       </c>
-      <c r="D21" s="11">
+      <c r="E16" s="12">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="9">
+      <c r="F16" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="16"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="10">
         <v>1</v>
       </c>
-      <c r="C22" s="10">
+      <c r="D17" s="11">
         <v>180</v>
       </c>
-      <c r="D22" s="11">
+      <c r="E17" s="12">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-      <c r="E22" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="12" t="s">
+      <c r="F17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="10">
+        <v>2</v>
+      </c>
+      <c r="D18" s="11">
+        <v>48</v>
+      </c>
+      <c r="E18" s="12">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="G22" s="13" t="s">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="9">
-        <v>2</v>
-      </c>
-      <c r="C23" s="10">
+      <c r="C19" s="10">
+        <v>1</v>
+      </c>
+      <c r="D19" s="11">
         <v>60</v>
       </c>
-      <c r="D23" s="11">
-        <f t="shared" si="1"/>
-        <v>120</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="9">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10">
-        <v>60</v>
-      </c>
-      <c r="D24" s="11">
+      <c r="E19" s="12">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="12" t="s">
+      <c r="F19" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="9">
+      <c r="C20" s="10">
         <v>1</v>
       </c>
-      <c r="C25" s="10">
+      <c r="D20" s="11">
         <v>50</v>
       </c>
-      <c r="D25" s="11">
+      <c r="E20" s="12">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="12" t="s">
+      <c r="F20" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="9">
+      <c r="C21" s="10">
         <v>2</v>
       </c>
-      <c r="C26" s="10">
+      <c r="D21" s="11">
         <v>10</v>
       </c>
-      <c r="D26" s="11">
+      <c r="E21" s="12">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="12"/>
-      <c r="G26" s="13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="9">
+      <c r="F21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="13"/>
+      <c r="H21" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="10">
         <v>2</v>
       </c>
-      <c r="C27" s="10">
+      <c r="D22" s="11">
         <v>10</v>
       </c>
-      <c r="D27" s="11">
+      <c r="E22" s="12">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="12" t="s">
+      <c r="F22" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="17"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18">
+        <f>SUM(E14:E22)</f>
+        <v>1716</v>
+      </c>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="15"/>
+      <c r="B26" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="C26" s="10">
+        <v>1</v>
+      </c>
+      <c r="D26" s="11">
+        <v>328</v>
+      </c>
+      <c r="E26" s="12">
+        <f>C26*D26</f>
+        <v>328</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="13"/>
+      <c r="H26" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16">
-        <f>SUM(D19:D27)</f>
-        <v>1740</v>
-      </c>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="8" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18">
+        <f>SUM(E26:E26)</f>
+        <v>328</v>
+      </c>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B31" s="9">
-        <v>2</v>
-      </c>
-      <c r="C31" s="10">
-        <v>300</v>
-      </c>
-      <c r="D31" s="11">
-        <f>B31*C31</f>
-        <v>600</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="12" t="s">
+      <c r="C29" s="20"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21" t="e">
+        <f>E11+#REF!+E23+E27</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="16"/>
+      <c r="B32" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G31" s="25" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
+      <c r="C32" s="10">
+        <v>1</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
+        <f t="shared" ref="E32:E40" si="2">C32*D32</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B32" s="9">
-        <v>1</v>
-      </c>
-      <c r="C32" s="10">
-        <v>90</v>
-      </c>
-      <c r="D32" s="11">
-        <f>B32*C32</f>
-        <v>90</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="12"/>
       <c r="G32" s="13" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16">
-        <f>SUM(D31:D32)</f>
-        <v>690</v>
-      </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="18" t="s">
+      <c r="H32" s="16"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="16"/>
+      <c r="B33" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="18"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19">
-        <f>D11+D16+D28+D33</f>
-        <v>3017</v>
-      </c>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="8" t="s">
+      <c r="C33" s="10">
+        <v>1</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G33" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="9">
+      <c r="H33" s="16"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="16"/>
+      <c r="B34" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="10">
+        <v>2</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H34" s="16"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="16"/>
+      <c r="B35" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" s="10">
+        <v>2</v>
+      </c>
+      <c r="D35" s="9">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="H35" s="16"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="16"/>
+      <c r="B36" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="10">
         <v>1</v>
       </c>
-      <c r="C38" s="8">
-        <v>0</v>
-      </c>
-      <c r="D38" s="8">
-        <f t="shared" ref="D38:D46" si="2">B38*C38</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G38" s="14"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="9">
+      <c r="D36" s="9">
+        <v>0</v>
+      </c>
+      <c r="E36" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="H36" s="16"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="16"/>
+      <c r="B37" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="10">
         <v>1</v>
       </c>
-      <c r="C39" s="8">
-        <v>0</v>
-      </c>
-      <c r="D39" s="8">
+      <c r="D37" s="9">
+        <v>0</v>
+      </c>
+      <c r="E37" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E39" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39" s="14"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="9">
-        <v>2</v>
-      </c>
-      <c r="C40" s="8">
-        <v>0</v>
-      </c>
-      <c r="D40" s="8">
+      <c r="F37" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H37" s="16"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="16"/>
+      <c r="B38" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="10">
+        <v>1</v>
+      </c>
+      <c r="D38" s="9">
+        <v>0</v>
+      </c>
+      <c r="E38" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E40" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G40" s="14"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B41" s="9">
-        <v>2</v>
-      </c>
-      <c r="C41" s="8">
-        <v>0</v>
-      </c>
-      <c r="D41" s="8">
+      <c r="F38" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H38" s="16"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="16"/>
+      <c r="B39" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="10">
+        <v>1</v>
+      </c>
+      <c r="D39" s="9">
+        <v>0</v>
+      </c>
+      <c r="E39" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E41" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G41" s="14"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B42" s="9">
-        <v>1</v>
-      </c>
-      <c r="C42" s="8">
-        <v>0</v>
-      </c>
-      <c r="D42" s="8">
+      <c r="F39" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G39" s="13"/>
+      <c r="H39" s="16"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="16"/>
+      <c r="B40" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" s="10">
+        <v>4</v>
+      </c>
+      <c r="D40" s="9">
+        <v>0</v>
+      </c>
+      <c r="E40" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E42" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G42" s="14"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" s="9">
-        <v>1</v>
-      </c>
-      <c r="C43" s="8">
-        <v>0</v>
-      </c>
-      <c r="D43" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E43" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G43" s="14"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="8" t="s">
+      <c r="F40" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G40" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B44" s="9">
-        <v>1</v>
-      </c>
-      <c r="C44" s="8">
-        <v>0</v>
-      </c>
-      <c r="D44" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E44" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F44" s="12" t="s">
+      <c r="H40" s="16"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="G44" s="14"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="8" t="s">
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B44" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="9">
-        <v>1</v>
-      </c>
-      <c r="C45" s="8">
-        <v>0</v>
-      </c>
-      <c r="D45" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E45" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F45" s="12"/>
-      <c r="G45" s="14"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="8" t="s">
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B45" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="B46" s="9">
-        <v>4</v>
-      </c>
-      <c r="C46" s="8">
-        <v>0</v>
-      </c>
-      <c r="D46" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E46" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F46" s="12" t="s">
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B46" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="G46" s="14"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" s="22" t="s">
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="25" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" s="23" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="25" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" s="23" t="s">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B49" s="25" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" s="23" t="s">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B50" s="25" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" s="23" t="s">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B51" s="25" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" s="23" t="s">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B52" s="25" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" s="23" t="s">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B53" s="25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" s="23" t="s">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B54" s="25" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" s="23" t="s">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B55" s="25" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" s="23" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" s="23" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="G9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="G14" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="G19" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="G20" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="G22" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="G24" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="G25" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="G26" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="G27" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="G31" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="G32" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="G23" r:id="rId14" xr:uid="{5BB78907-871B-7E4A-BC38-ECB9633DDA26}"/>
+    <hyperlink ref="H8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="H9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="H14" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="H15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="H17" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="H18" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="H19" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="H20" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="H21" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="H22" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="H26" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Alinacak Malzemeler Ucuz.xlsx
+++ b/Alinacak Malzemeler Ucuz.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erayfazilordanuc/Projects/RC Uçak/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\RC Plane\rc-plane\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE42DAA-39BF-F84F-85AC-7AFC7AD7A5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99916FEE-2807-4F37-AFD6-5CF819C64ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Malzeme Listesi" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="88">
   <si>
     <t>Fotoblok RC Trainer - Alinacak Malzemeler</t>
   </si>
@@ -182,9 +182,6 @@
     <t>STM32F411CEU6 Black Pill</t>
   </si>
   <si>
-    <t>https://www.f1depo.com/urun/stm32f411ceu6-black-pill-100mhz-512kb-gelistirme-karti</t>
-  </si>
-  <si>
     <t>GENEL TOPLAM (satin alinacak)</t>
   </si>
   <si>
@@ -291,6 +288,18 @@
   </si>
   <si>
     <t>ELINDE MEVCUT - SATIN ALINMAYACAK</t>
+  </si>
+  <si>
+    <t>https://www.robotistan.com/stm32f103c8t6a-gelistirme-karti</t>
+  </si>
+  <si>
+    <t>ST-Link V2 Mini St Programlayıcı</t>
+  </si>
+  <si>
+    <t>https://www.robotistan.com/st-link-v2-mini-st-programlayici-klon?language=tr&amp;h=1bb5f3ab&amp;_sgm_campaign=scn_bfbf0d077c000&amp;_sgm_source=12386&amp;_sgm_action=click</t>
+  </si>
+  <si>
+    <t>Alındı</t>
   </si>
 </sst>
 </file>
@@ -300,7 +309,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot; TL&quot;"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -405,6 +414,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -474,8 +491,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -501,9 +519,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -514,8 +529,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -778,8 +795,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H56"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -791,27 +808,27 @@
     <col min="8" max="8" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
@@ -837,10 +854,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="7"/>
@@ -849,7 +866,7 @@
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>4</v>
       </c>
@@ -876,7 +893,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>4</v>
       </c>
@@ -903,7 +920,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>4</v>
       </c>
@@ -921,36 +938,36 @@
         <v>80</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17" t="s">
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18">
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17">
         <f>SUM(E8:E10)</f>
         <v>447</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="7"/>
@@ -959,7 +976,7 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>4</v>
       </c>
@@ -977,7 +994,7 @@
         <v>800</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>23</v>
@@ -986,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
@@ -1004,7 +1021,7 @@
         <v>430</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>26</v>
@@ -1013,7 +1030,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>4</v>
       </c>
@@ -1031,14 +1048,14 @@
         <v>60</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="16"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H16" s="15"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>4</v>
       </c>
@@ -1056,7 +1073,7 @@
         <v>180</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>31</v>
@@ -1065,7 +1082,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>4</v>
       </c>
@@ -1083,7 +1100,7 @@
         <v>96</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>34</v>
@@ -1092,7 +1109,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>4</v>
       </c>
@@ -1110,7 +1127,7 @@
         <v>60</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>37</v>
@@ -1119,7 +1136,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>4</v>
       </c>
@@ -1137,7 +1154,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>40</v>
@@ -1146,7 +1163,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>4</v>
       </c>
@@ -1164,14 +1181,14 @@
         <v>20</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>4</v>
       </c>
@@ -1189,7 +1206,7 @@
         <v>20</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>45</v>
@@ -1198,29 +1215,29 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18">
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17">
         <f>SUM(E14:E22)</f>
         <v>1716</v>
       </c>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="7"/>
@@ -1229,8 +1246,10 @@
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="15"/>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="B26" s="9" t="s">
         <v>47</v>
       </c>
@@ -1238,93 +1257,92 @@
         <v>1</v>
       </c>
       <c r="D26" s="11">
-        <v>328</v>
+        <v>182</v>
       </c>
       <c r="E26" s="12">
         <f>C26*D26</f>
-        <v>328</v>
+        <v>182</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="G26" s="13"/>
-      <c r="H26" s="14" t="s">
+      <c r="H26" s="25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="10">
+        <v>1</v>
+      </c>
+      <c r="D27" s="11">
+        <v>125</v>
+      </c>
+      <c r="E27" s="12"/>
+      <c r="F27" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="13"/>
+      <c r="H27" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17">
+        <f>SUM(E26:E26)</f>
+        <v>182</v>
+      </c>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="19"/>
+      <c r="B30" s="19" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18">
-        <f>SUM(E26:E26)</f>
-        <v>328</v>
-      </c>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20" t="s">
+      <c r="C30" s="19"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20">
+        <f>E11+E23+E28</f>
+        <v>2345</v>
+      </c>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="15"/>
+      <c r="B33" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21" t="e">
-        <f>E11+#REF!+E23+E27</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="22"/>
-      <c r="B31" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="16"/>
-      <c r="B32" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="10">
-        <v>1</v>
-      </c>
-      <c r="D32" s="9">
-        <v>0</v>
-      </c>
-      <c r="E32" s="9">
-        <f t="shared" ref="E32:E40" si="2">C32*D32</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G32" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H32" s="16"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="16"/>
-      <c r="B33" s="9" t="s">
-        <v>53</v>
       </c>
       <c r="C33" s="10">
         <v>1</v>
@@ -1333,24 +1351,24 @@
         <v>0</v>
       </c>
       <c r="E33" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="23" t="s">
+        <f t="shared" ref="E33:E41" si="2">C33*D33</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G33" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="H33" s="16"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="16"/>
+      <c r="H33" s="15"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="15"/>
       <c r="B34" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C34" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" s="9">
         <v>0</v>
@@ -1359,18 +1377,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F34" s="23" t="s">
-        <v>51</v>
+      <c r="F34" s="22" t="s">
+        <v>50</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="H34" s="16"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="16"/>
+        <v>53</v>
+      </c>
+      <c r="H34" s="15"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="15"/>
       <c r="B35" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C35" s="10">
         <v>2</v>
@@ -1382,21 +1400,21 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F35" s="23" t="s">
-        <v>51</v>
+      <c r="F35" s="22" t="s">
+        <v>50</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="H35" s="16"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="16"/>
+        <v>55</v>
+      </c>
+      <c r="H35" s="15"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
       <c r="B36" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C36" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" s="9">
         <v>0</v>
@@ -1405,18 +1423,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F36" s="23" t="s">
-        <v>51</v>
+      <c r="F36" s="22" t="s">
+        <v>50</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="H36" s="16"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="16"/>
+        <v>57</v>
+      </c>
+      <c r="H36" s="15"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="15"/>
       <c r="B37" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C37" s="10">
         <v>1</v>
@@ -1428,18 +1446,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F37" s="23" t="s">
-        <v>51</v>
+      <c r="F37" s="22" t="s">
+        <v>50</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="H37" s="16"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="16"/>
+        <v>59</v>
+      </c>
+      <c r="H37" s="15"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="15"/>
       <c r="B38" s="9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C38" s="10">
         <v>1</v>
@@ -1451,18 +1469,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F38" s="23" t="s">
-        <v>51</v>
+      <c r="F38" s="22" t="s">
+        <v>50</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H38" s="16"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="16"/>
+        <v>61</v>
+      </c>
+      <c r="H38" s="15"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="15"/>
       <c r="B39" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C39" s="10">
         <v>1</v>
@@ -1474,19 +1492,21 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F39" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G39" s="13"/>
-      <c r="H39" s="16"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="16"/>
+      <c r="F39" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H39" s="15"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="15"/>
       <c r="B40" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C40" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D40" s="9">
         <v>0</v>
@@ -1495,77 +1515,98 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F40" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G40" s="13" t="s">
+      <c r="F40" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40" s="13"/>
+      <c r="H40" s="15"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="15"/>
+      <c r="B41" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="10">
+        <v>4</v>
+      </c>
+      <c r="D41" s="9">
+        <v>0</v>
+      </c>
+      <c r="E41" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H41" s="15"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="H40" s="16"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B43" s="24" t="s">
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="24" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B44" s="25" t="s">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="24" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B45" s="25" t="s">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="24" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="25" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B48" s="24" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="25" t="s">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B49" s="24" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="25" t="s">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B50" s="24" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B49" s="25" t="s">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B51" s="24" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B50" s="25" t="s">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B52" s="24" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B51" s="25" t="s">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B53" s="24" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B52" s="25" t="s">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B54" s="24" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B53" s="25" t="s">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B55" s="24" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B54" s="25" t="s">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B56" s="24" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B55" s="25" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1583,6 +1624,6 @@
     <hyperlink ref="H26" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId12"/>
 </worksheet>
 </file>